--- a/LCAResults/SCPLCAResults_KPIs.xlsx
+++ b/LCAResults/SCPLCAResults_KPIs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://api.box.com/wopi/files/2410751457098/WOPIServiceId_TP_BOX_2/WOPIUserId_-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{C01098CF-3EA0-4C6C-9564-B692B9CF1869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01E9EF94-435D-4F3C-8EA0-2FBBB76BE531}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{C01098CF-3EA0-4C6C-9564-B692B9CF1869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11412C4E-9AC6-4A9E-B0E9-4D79242EA22A}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7CE15DA7-D44F-409E-B74A-9F763C658849}"/>
+    <workbookView xWindow="-14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{7CE15DA7-D44F-409E-B74A-9F763C658849}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -518,13 +518,13 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D2">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="E2">
-        <v>518</v>
+        <v>111</v>
       </c>
       <c r="F2">
         <v>187</v>
@@ -538,13 +538,13 @@
         <v>17</v>
       </c>
       <c r="C3">
-        <v>7.3</v>
+        <v>-0.5</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>1.8</v>
       </c>
       <c r="E3">
-        <v>166</v>
+        <v>12</v>
       </c>
       <c r="F3">
         <v>60</v>
@@ -558,13 +558,13 @@
         <v>18</v>
       </c>
       <c r="C4">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="D4">
-        <v>0.25</v>
+        <v>0.02</v>
       </c>
       <c r="E4">
-        <v>1.9</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="F4">
         <v>0.8</v>
@@ -578,13 +578,13 @@
         <v>19</v>
       </c>
       <c r="C5" s="1">
-        <v>7.7000000000000008E-6</v>
+        <v>2.3E-6</v>
       </c>
       <c r="D5" s="1">
-        <v>1.5999999999999999E-5</v>
-      </c>
-      <c r="E5">
-        <v>1E-4</v>
+        <v>2.3E-6</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="F5" s="1">
         <v>3.0000000000000001E-5</v>
@@ -604,7 +604,7 @@
         <v>-21</v>
       </c>
       <c r="E6">
-        <v>-160</v>
+        <v>-162</v>
       </c>
       <c r="F6">
         <v>57</v>
@@ -618,13 +618,13 @@
         <v>21</v>
       </c>
       <c r="C7">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D7">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E7">
-        <v>0.38</v>
+        <v>0.23</v>
       </c>
       <c r="F7">
         <v>4.3</v>
@@ -658,13 +658,13 @@
         <v>21</v>
       </c>
       <c r="C9">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="D9">
-        <v>6.6</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E9">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="F9">
         <v>695</v>
@@ -678,13 +678,13 @@
         <v>23</v>
       </c>
       <c r="C10">
-        <v>7.0000000000000007E-2</v>
+        <v>0.05</v>
       </c>
       <c r="D10">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="E10">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="F10">
         <v>0.27</v>
@@ -698,13 +698,13 @@
         <v>21</v>
       </c>
       <c r="C11">
-        <v>28</v>
+        <v>3.9</v>
       </c>
       <c r="D11">
-        <v>71</v>
+        <v>6.3</v>
       </c>
       <c r="E11">
-        <v>530</v>
+        <v>44</v>
       </c>
       <c r="F11">
         <v>627</v>
